--- a/reports/test7_summary.xlsx
+++ b/reports/test7_summary.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,6 +66,18 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="5">
@@ -130,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -151,11 +163,23 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -231,6 +255,941 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="13"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Flory Calibration Curves (log-log Plot)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Table 1'!E22</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1F497D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Table 1'!$F$21:$G$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Table 1'!$F$22:$G$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Table 1'!E23</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Table 1'!$F$21:$G$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Table 1'!$F$23:$G$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Table 1'!E24</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="9BBB59"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Table 1'!$F$21:$G$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Table 1'!$F$24:$G$24</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Table 1'!E25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Table 1'!$F$21:$G$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Table 1'!$F$25:$G$25</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Table 1'!E26</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="F79646"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Table 1'!$F$21:$G$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Table 1'!$F$26:$G$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>log(M / g mol⁻¹)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="-8.960000000000001"/>
+          <min val="-11.07"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>log(D / m² s⁻¹)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="13"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Flory Calibration Curves (log-log Plot)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Table 3'!E22</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1F497D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Table 3'!$F$21:$G$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Table 3'!$F$22:$G$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Table 3'!E23</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Table 3'!$F$21:$G$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Table 3'!$F$23:$G$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Table 3'!E24</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="9BBB59"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Table 3'!$F$21:$G$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Table 3'!$F$24:$G$24</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Table 3'!E25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Table 3'!$F$21:$G$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Table 3'!$F$25:$G$25</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>log(M / g mol⁻¹)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="-8.960000000000001"/>
+          <min val="-11.21"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>log(D / m² s⁻¹)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="13"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Flory Calibration Curves (log-log Plot)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Table 6'!E22</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1F497D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Table 6'!$F$21:$G$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Table 6'!$F$22:$G$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Table 6'!E23</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Table 6'!$F$21:$G$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Table 6'!$F$23:$G$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Table 6'!E24</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="9BBB59"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Table 6'!$F$21:$G$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Table 6'!$F$24:$G$24</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>log(M / g mol⁻¹)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="-9.08"/>
+          <min val="-11.23"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>log(D / m² s⁻¹)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="13"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Flory Calibration Curves (log-log Plot)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Table 7'!E22</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1F497D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Table 7'!$F$21:$G$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Table 7'!$F$22:$G$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>log(M / g mol⁻¹)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="-9"/>
+          <min val="-10.51"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>log(D / m² s⁻¹)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -522,14 +1481,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
@@ -537,7 +1496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>A fast and e ffi cient way of obtaining the average molecular weight of block copolymers via DOSY †</t>
+          <t>test7</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -576,11 +1535,7 @@
           <t>Authors</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Pieter-Jan Voorter, Manfred Wagner, Christine Rosenauer, Jinhuo Dai, Priya Subramanian, Alasdair McKay, Neil R. Cameron, Jasper J. Michels, Tanja Junkers</t>
-        </is>
-      </c>
+      <c r="B5" s="6" t="inlineStr"/>
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="n"/>
@@ -593,11 +1548,7 @@
           <t>DOI</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>10.1039/d3py01075a</t>
-        </is>
-      </c>
+      <c r="B6" s="6" t="inlineStr"/>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
@@ -788,7 +1739,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>EXTRACTED RAW TABLE DATA</t>
+          <t>FLORY PARAMETERS (INTERPRETATION)</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -799,115 +1750,318 @@
       <c r="G20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr"/>
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Polymer</t>
+        </is>
+      </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
+          <t>Solvent</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>c_value (log Constant)</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>v_value (Scaling Exponent)</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>pMMA</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Toluene</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>-8.109999999999999</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>pMMA in Toluene</t>
+        </is>
+      </c>
+      <c r="F22" s="15">
+        <f>C22-D22*3</f>
+        <v/>
+      </c>
+      <c r="G22" s="15">
+        <f>C22-D22*6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>pMMA</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Benzene</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>-7.91</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>pMMA in Benzene</t>
+        </is>
+      </c>
+      <c r="F23" s="15">
+        <f>C23-D23*3</f>
+        <v/>
+      </c>
+      <c r="G23" s="15">
+        <f>C23-D23*6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>pMMA</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>sAcetone</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>-7.74</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>pMMA in sAcetone</t>
+        </is>
+      </c>
+      <c r="F24" s="15">
+        <f>C24-D24*3</f>
+        <v/>
+      </c>
+      <c r="G24" s="15">
+        <f>C24-D24*6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>pMMA</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>THF</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>-8.02</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>pMMA in THF</t>
+        </is>
+      </c>
+      <c r="F25" s="15">
+        <f>C25-D25*3</f>
+        <v/>
+      </c>
+      <c r="G25" s="15">
+        <f>C25-D25*6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>pMMA</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>D x η corrected</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>-8.27</v>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>pMMA in D x η corrected</t>
+        </is>
+      </c>
+      <c r="F26" s="15">
+        <f>C26-D26*3</f>
+        <v/>
+      </c>
+      <c r="G26" s="15">
+        <f>C26-D26*6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>EXTRACTED RAW TABLE DATA</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr"/>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
           <t>Sample</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>lg( b ′ /m 2 s - 1 )</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>v</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="10" t="n">
+    <row r="31">
+      <c r="A31" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>Toluene</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>- 8.11</t>
         </is>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D31" s="13" t="n">
         <v>0.43</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="n">
+    <row r="32">
+      <c r="A32" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>Benzene</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>- 7.91</t>
         </is>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D32" s="13" t="n">
         <v>0.48</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="10" t="n">
+    <row r="33">
+      <c r="A33" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Acetone</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>- 7.74</t>
         </is>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D33" s="13" t="n">
         <v>0.44</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="n">
+    <row r="34">
+      <c r="A34" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>THF</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>- 8.02</t>
         </is>
       </c>
-      <c r="D25" s="10" t="n">
+      <c r="D34" s="13" t="n">
         <v>0.43</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="10" t="n">
+    <row r="35">
+      <c r="A35" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>D × η corrected</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>- 8.27</t>
         </is>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D35" s="13" t="n">
         <v>0.45</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="B16:G16"/>
     <mergeCell ref="B10:G10"/>
@@ -920,12 +2074,14 @@
     <mergeCell ref="B8:G8"/>
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="B18:G18"/>
+    <mergeCell ref="A29:G29"/>
     <mergeCell ref="B15:G15"/>
     <mergeCell ref="B7:G7"/>
     <mergeCell ref="B11:G11"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -950,7 +2106,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>A fast and e ffi cient way of obtaining the average molecular weight of block copolymers via DOSY †</t>
+          <t>test7</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -989,11 +2145,7 @@
           <t>Authors</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Pieter-Jan Voorter, Manfred Wagner, Christine Rosenauer, Jinhuo Dai, Priya Subramanian, Alasdair McKay, Neil R. Cameron, Jasper J. Michels, Tanja Junkers</t>
-        </is>
-      </c>
+      <c r="B5" s="6" t="inlineStr"/>
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="n"/>
@@ -1006,11 +2158,7 @@
           <t>DOI</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>10.1039/d3py01075a</t>
-        </is>
-      </c>
+      <c r="B6" s="6" t="inlineStr"/>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
@@ -1239,122 +2387,122 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>pBA35</t>
         </is>
       </c>
-      <c r="C22" s="10" t="n">
+      <c r="C22" s="13" t="n">
         <v>4500</v>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D22" s="13" t="n">
         <v>6800</v>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="E22" s="13" t="n">
         <v>1.07</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n">
+      <c r="A23" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>pBA55</t>
         </is>
       </c>
-      <c r="C23" s="10" t="n">
+      <c r="C23" s="13" t="n">
         <v>6100</v>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D23" s="13" t="n">
         <v>7800</v>
       </c>
-      <c r="E23" s="10" t="n">
+      <c r="E23" s="13" t="n">
         <v>1.14</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n">
+      <c r="A24" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>pBA60</t>
         </is>
       </c>
-      <c r="C24" s="10" t="n">
+      <c r="C24" s="13" t="n">
         <v>5400</v>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="13" t="n">
         <v>7200</v>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="E24" s="13" t="n">
         <v>1.12</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n">
+      <c r="A25" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>pBA75</t>
         </is>
       </c>
-      <c r="C25" s="10" t="n">
+      <c r="C25" s="13" t="n">
         <v>9700</v>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>12 200</t>
         </is>
       </c>
-      <c r="E25" s="10" t="n">
+      <c r="E25" s="13" t="n">
         <v>1.11</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>pBA80</t>
         </is>
       </c>
-      <c r="C26" s="10" t="n">
+      <c r="C26" s="13" t="n">
         <v>7400</v>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D26" s="13" t="n">
         <v>8600</v>
       </c>
-      <c r="E26" s="10" t="n">
+      <c r="E26" s="13" t="n">
         <v>1.09</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n">
+      <c r="A27" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>pBA100</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>11 800</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>10 600</t>
         </is>
       </c>
-      <c r="E27" s="10" t="n">
+      <c r="E27" s="13" t="n">
         <v>1.19</v>
       </c>
     </row>
@@ -1387,14 +2535,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1402,7 +2550,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>A fast and e ffi cient way of obtaining the average molecular weight of block copolymers via DOSY †</t>
+          <t>test7</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1441,11 +2589,7 @@
           <t>Authors</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Pieter-Jan Voorter, Manfred Wagner, Christine Rosenauer, Jinhuo Dai, Priya Subramanian, Alasdair McKay, Neil R. Cameron, Jasper J. Michels, Tanja Junkers</t>
-        </is>
-      </c>
+      <c r="B5" s="6" t="inlineStr"/>
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="n"/>
@@ -1458,11 +2602,7 @@
           <t>DOI</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>10.1039/d3py01075a</t>
-        </is>
-      </c>
+      <c r="B6" s="6" t="inlineStr"/>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
@@ -1653,7 +2793,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>EXTRACTED RAW TABLE DATA</t>
+          <t>FLORY PARAMETERS (INTERPRETATION)</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -1664,97 +2804,269 @@
       <c r="G20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr"/>
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Polymer</t>
+        </is>
+      </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
+          <t>Solvent</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>c_value (log Constant)</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>v_value (Scaling Exponent)</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>poly(butyl acrylate)</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Benzene</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>-7.83</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>poly(butyl acrylate) in Benzene</t>
+        </is>
+      </c>
+      <c r="F22" s="15">
+        <f>C22-D22*3</f>
+        <v/>
+      </c>
+      <c r="G22" s="15">
+        <f>C22-D22*6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>poly(butyl acrylate)</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Acetone</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>-7.56</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>poly(butyl acrylate) in Acetone</t>
+        </is>
+      </c>
+      <c r="F23" s="15">
+        <f>C23-D23*3</f>
+        <v/>
+      </c>
+      <c r="G23" s="15">
+        <f>C23-D23*6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>poly(butyl acrylate)</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Chloroform</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>-7.86</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>poly(butyl acrylate) in Chloroform</t>
+        </is>
+      </c>
+      <c r="F24" s="15">
+        <f>C24-D24*3</f>
+        <v/>
+      </c>
+      <c r="G24" s="15">
+        <f>C24-D24*6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>poly(butyl acrylate)</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>D x η corrected</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>-8.050000000000001</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>poly(butyl acrylate) in D x η corrected</t>
+        </is>
+      </c>
+      <c r="F25" s="15">
+        <f>C25-D25*3</f>
+        <v/>
+      </c>
+      <c r="G25" s="15">
+        <f>C25-D25*6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>EXTRACTED RAW TABLE DATA</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr"/>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
           <t>Sample</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>lg( b ′ /m 2 s - 1 )</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>v</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="10" t="n">
+    <row r="30">
+      <c r="A30" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Benzene</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>- 7.83</t>
         </is>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D30" s="13" t="n">
         <v>0.51</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="n">
+    <row r="31">
+      <c r="A31" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>Acetone</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>- 7.56</t>
         </is>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D31" s="13" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="10" t="n">
+    <row r="32">
+      <c r="A32" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>Chloroform</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>- 7.86</t>
         </is>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D32" s="13" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="n">
+    <row r="33">
+      <c r="A33" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>D × η corrected</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>- 8.05</t>
         </is>
       </c>
-      <c r="D25" s="10" t="n">
+      <c r="D33" s="13" t="n">
         <v>0.51</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="B16:G16"/>
     <mergeCell ref="B10:G10"/>
@@ -1767,12 +3079,14 @@
     <mergeCell ref="B8:G8"/>
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="B18:G18"/>
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="B15:G15"/>
     <mergeCell ref="B7:G7"/>
     <mergeCell ref="B11:G11"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1797,7 +3111,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>A fast and e ffi cient way of obtaining the average molecular weight of block copolymers via DOSY †</t>
+          <t>test7</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1836,11 +3150,7 @@
           <t>Authors</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Pieter-Jan Voorter, Manfred Wagner, Christine Rosenauer, Jinhuo Dai, Priya Subramanian, Alasdair McKay, Neil R. Cameron, Jasper J. Michels, Tanja Junkers</t>
-        </is>
-      </c>
+      <c r="B5" s="6" t="inlineStr"/>
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="n"/>
@@ -1853,11 +3163,7 @@
           <t>DOI</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>10.1039/d3py01075a</t>
-        </is>
-      </c>
+      <c r="B6" s="6" t="inlineStr"/>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
@@ -2087,270 +3393,270 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>pBA35-pMA30</t>
         </is>
       </c>
-      <c r="C22" s="10" t="n">
+      <c r="C22" s="13" t="n">
         <v>6100</v>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D22" s="13" t="n">
         <v>7700</v>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="E22" s="13" t="n">
         <v>1.15</v>
       </c>
-      <c r="F22" s="10" t="n">
+      <c r="F22" s="13" t="n">
         <v>6060</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n">
+      <c r="A23" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>pBA35-pMA60</t>
         </is>
       </c>
-      <c r="C23" s="10" t="n">
+      <c r="C23" s="13" t="n">
         <v>8000</v>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>10 200</t>
         </is>
       </c>
-      <c r="E23" s="10" t="n">
+      <c r="E23" s="13" t="n">
         <v>1.22</v>
       </c>
-      <c r="F23" s="10" t="n">
+      <c r="F23" s="13" t="n">
         <v>7710</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n">
+      <c r="A24" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>pBA35-pMA90</t>
         </is>
       </c>
-      <c r="C24" s="10" t="n">
+      <c r="C24" s="13" t="n">
         <v>8900</v>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="13" t="n">
         <v>9600</v>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="E24" s="13" t="n">
         <v>1.1</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F24" s="13" t="n">
         <v>8350</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n">
+      <c r="A25" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>pBA35-pMA120</t>
         </is>
       </c>
-      <c r="C25" s="10" t="n">
+      <c r="C25" s="13" t="n">
         <v>9500</v>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>11 100</t>
         </is>
       </c>
-      <c r="E25" s="10" t="n">
+      <c r="E25" s="13" t="n">
         <v>1.16</v>
       </c>
-      <c r="F25" s="10" t="n">
+      <c r="F25" s="13" t="n">
         <v>8690</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>pBA55-pMA30</t>
         </is>
       </c>
-      <c r="C26" s="10" t="n">
+      <c r="C26" s="13" t="n">
         <v>7600</v>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D26" s="13" t="n">
         <v>9200</v>
       </c>
-      <c r="E26" s="10" t="n">
+      <c r="E26" s="13" t="n">
         <v>1.16</v>
       </c>
-      <c r="F26" s="10" t="n">
+      <c r="F26" s="13" t="n">
         <v>7330</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n">
+      <c r="A27" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>pBA55-pMA60</t>
         </is>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C27" s="13" t="n">
         <v>8700</v>
       </c>
-      <c r="D27" s="10" t="n">
+      <c r="D27" s="13" t="n">
         <v>9500</v>
       </c>
-      <c r="E27" s="10" t="n">
+      <c r="E27" s="13" t="n">
         <v>1.16</v>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="F27" s="13" t="n">
         <v>8460</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="n">
+      <c r="A28" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>pBA55-pMA90</t>
         </is>
       </c>
-      <c r="C28" s="10" t="n">
+      <c r="C28" s="13" t="n">
         <v>9400</v>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>11 000</t>
         </is>
       </c>
-      <c r="E28" s="10" t="n">
+      <c r="E28" s="13" t="n">
         <v>1.12</v>
       </c>
-      <c r="F28" s="10" t="n">
+      <c r="F28" s="13" t="n">
         <v>8930</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
+      <c r="A29" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>pBA55-pMA120</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>10 200</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>11 100</t>
         </is>
       </c>
-      <c r="E29" s="10" t="n">
+      <c r="E29" s="13" t="n">
         <v>1.16</v>
       </c>
-      <c r="F29" s="10" t="n">
+      <c r="F29" s="13" t="n">
         <v>9450</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n">
+      <c r="A30" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>pBA75-pMA60</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>11 200</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>12 500</t>
         </is>
       </c>
-      <c r="E30" s="10" t="n">
+      <c r="E30" s="13" t="n">
         <v>1.15</v>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F30" s="12" t="inlineStr">
         <is>
           <t>10 960</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n">
+      <c r="A31" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>pBA75-pMA90</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>13 800</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>16 100</t>
         </is>
       </c>
-      <c r="E31" s="10" t="n">
+      <c r="E31" s="13" t="n">
         <v>1.15</v>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F31" s="12" t="inlineStr">
         <is>
           <t>13 310</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n">
+      <c r="A32" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>pBA75-pMA120</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>14 200</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>14 700</t>
         </is>
       </c>
-      <c r="E32" s="10" t="n">
+      <c r="E32" s="13" t="n">
         <v>1.12</v>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="12" t="inlineStr">
         <is>
           <t>13 780</t>
         </is>
@@ -2400,7 +3706,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>A fast and e ffi cient way of obtaining the average molecular weight of block copolymers via DOSY †</t>
+          <t>test7</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2439,11 +3745,7 @@
           <t>Authors</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Pieter-Jan Voorter, Manfred Wagner, Christine Rosenauer, Jinhuo Dai, Priya Subramanian, Alasdair McKay, Neil R. Cameron, Jasper J. Michels, Tanja Junkers</t>
-        </is>
-      </c>
+      <c r="B5" s="6" t="inlineStr"/>
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="n"/>
@@ -2456,11 +3758,7 @@
           <t>DOI</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>10.1039/d3py01075a</t>
-        </is>
-      </c>
+      <c r="B6" s="6" t="inlineStr"/>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
@@ -2689,134 +3987,134 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>pPEGMEA15</t>
         </is>
       </c>
-      <c r="C22" s="10" t="n">
+      <c r="C22" s="13" t="n">
         <v>6500</v>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D22" s="13" t="n">
         <v>7800</v>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="E22" s="13" t="n">
         <v>1.33</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n">
+      <c r="A23" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>pPEGMEA20</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>10 500</t>
         </is>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D23" s="13" t="n">
         <v>7800</v>
       </c>
-      <c r="E23" s="10" t="n">
+      <c r="E23" s="13" t="n">
         <v>1.23</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n">
+      <c r="A24" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>pPEGMEA40</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>16 200</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>10 100</t>
         </is>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="E24" s="13" t="n">
         <v>1.36</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n">
+      <c r="A25" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>pPEGMEA60</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>19 700</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>10 900</t>
         </is>
       </c>
-      <c r="E25" s="10" t="n">
+      <c r="E25" s="13" t="n">
         <v>1.37</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>pPEGMEA80</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>19 600</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>11 100</t>
         </is>
       </c>
-      <c r="E26" s="10" t="n">
+      <c r="E26" s="13" t="n">
         <v>1.35</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n">
+      <c r="A27" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>pPEGMEA100</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>19 800</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>11 600</t>
         </is>
       </c>
-      <c r="E27" s="10" t="n">
+      <c r="E27" s="13" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -2849,14 +4147,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2864,7 +4162,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>A fast and e ffi cient way of obtaining the average molecular weight of block copolymers via DOSY †</t>
+          <t>test7</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2903,11 +4201,7 @@
           <t>Authors</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Pieter-Jan Voorter, Manfred Wagner, Christine Rosenauer, Jinhuo Dai, Priya Subramanian, Alasdair McKay, Neil R. Cameron, Jasper J. Michels, Tanja Junkers</t>
-        </is>
-      </c>
+      <c r="B5" s="6" t="inlineStr"/>
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="n"/>
@@ -2920,11 +4214,7 @@
           <t>DOI</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>10.1039/d3py01075a</t>
-        </is>
-      </c>
+      <c r="B6" s="6" t="inlineStr"/>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
@@ -3115,7 +4405,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>EXTRACTED RAW TABLE DATA</t>
+          <t>FLORY PARAMETERS (INTERPRETATION)</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -3126,79 +4416,1091 @@
       <c r="G20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr"/>
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Polymer</t>
+        </is>
+      </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
+          <t>Solvent</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>c_value (log Constant)</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>v_value (Scaling Exponent)</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>pPEGMEA</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>-8.31</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>pPEGMEA in Water</t>
+        </is>
+      </c>
+      <c r="F22" s="15">
+        <f>C22-D22*3</f>
+        <v/>
+      </c>
+      <c r="G22" s="15">
+        <f>C22-D22*6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>pPEGMEA</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Acetone</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>-8.01</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>pPEGMEA in Acetone</t>
+        </is>
+      </c>
+      <c r="F23" s="15">
+        <f>C23-D23*3</f>
+        <v/>
+      </c>
+      <c r="G23" s="15">
+        <f>C23-D23*6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>pPEGMEA</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>D x η corrected</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>-8.390000000000001</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>pPEGMEA in D x η corrected</t>
+        </is>
+      </c>
+      <c r="F24" s="15">
+        <f>C24-D24*3</f>
+        <v/>
+      </c>
+      <c r="G24" s="15">
+        <f>C24-D24*6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>EXTRACTED RAW TABLE DATA</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr"/>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
           <t>Sample</t>
         </is>
       </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>lg( b ′ /m 2 s - 1 )</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>- 8.31</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>Acetone</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>- 8.01</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>D × η corrected</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>- 8.39</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="B6:G6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>test7</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>PAPER METADATA &amp; EXPERIMENTAL CONDITIONS</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Authors</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>DOI</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Temperature</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Pressure</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>pMMA, pPEGMEA, pMMA-pPEGMEA block copolymer, deuterated acetone, deuterated chloroform</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>MALLS and DOSY molecular weight measurements of pMMA homopolymers and pMMA-pPEGMEA block copolymers.</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Other Stats</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>MALLS Mw (g mol-1): 2630 - 135000, DOSYMW (g mol-1) (pMMA calibration): 2740 - 139730, DOSYMW (g mol-1) (pPEGMEA calibration): 1540 - 129610, DOSYMW (g mol-1) (pMMA-pPEGMEA joint calibration): 13810 - 115000</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>TABLE CATEGORISATION</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Contains Scientific Data</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Contains Raw Diffusion Data</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Contains Mark-Houwink Parameters</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Contains Flory Parameters</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Contains Polymer Diffusion Coefficients</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>FLORY PARAMETERS (INTERPRETATION)</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Polymer</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Solvent</t>
+        </is>
+      </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>lg( b ′ /m 2 s - 1 )</t>
+          <t>c_value (log Constant)</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>v</t>
-        </is>
+          <t>v_value (Scaling Exponent)</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>pMMA-pPEGMEA</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>deuterated acetone</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>-7.797</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>0.4355</v>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>pMMA-pPEGMEA in deuterated acetone</t>
+        </is>
+      </c>
+      <c r="F22" s="15">
+        <f>C22-D22*3</f>
+        <v/>
+      </c>
+      <c r="G22" s="15">
+        <f>C22-D22*6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>EXTRACTED RAW TABLE DATA</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr"/>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>MALLS. M w (g mol - 1 )</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>DOSYMW (g mol - 1 ) (pMMA)</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Error (%)</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>DOSYMW (g mol - 1 ) (pPEGMEA)</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>Error (%)</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>DOSYMW (g mol - 1 ) (pMMA-pPEGMEA)</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>Error (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>- 8.31</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="n">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="n">
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>pMMA25</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>2630</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>2740</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>1540</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>71</v>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>2160</v>
+      </c>
+      <c r="I27" s="13" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>Acetone</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>- 8.01</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="n">
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>pMMA45</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>4910</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>4970</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>3010</v>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>63</v>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>3950</v>
+      </c>
+      <c r="I28" s="13" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>D × η corrected</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>- 8.39</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>0.43</v>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>pMMA65</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>7010</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>7400</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>4710</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>49</v>
+      </c>
+      <c r="H29" s="13" t="n">
+        <v>5910</v>
+      </c>
+      <c r="I29" s="13" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>pMMA25-pPEGMEA25</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>10 600</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>14 690</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>10 200</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>11 810</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>pMMA25-pPEGMEA50</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>23 000</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>32 600</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>25 100</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>26 430</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>pMMA25-pPEGMEA75</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>45 400</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>56 160</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>46 340</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>45 780</t>
+        </is>
+      </c>
+      <c r="I32" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>pMMA45-pPEGMEA25</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>18 000</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>22 580</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>16 580</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>18 230</t>
+        </is>
+      </c>
+      <c r="I33" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>pMMA45-pPEGMEA50</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>34 500</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>43 860</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>35 070</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>35 670</t>
+        </is>
+      </c>
+      <c r="I34" s="13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>pMMA45-pPEGMEA75</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>68 400</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>78 110</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>67 250</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>63 900</t>
+        </is>
+      </c>
+      <c r="I35" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>pMMA65-pPEGMEA25</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>31 500</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>41 540</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>32 980</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>33 760</t>
+        </is>
+      </c>
+      <c r="I36" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>pMMA65-pPEGMEA50</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>91 100</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>90 450</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>79 350</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>84 100</t>
+        </is>
+      </c>
+      <c r="I37" s="13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>pMMA65-pPEGMEA75</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>135 000</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>139 730</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>129 610</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>115 000</t>
+        </is>
+      </c>
+      <c r="I38" s="13" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="B16:G16"/>
     <mergeCell ref="B10:G10"/>
@@ -3211,810 +5513,14 @@
     <mergeCell ref="B8:G8"/>
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="B18:G18"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="B15:G15"/>
     <mergeCell ref="B7:G7"/>
     <mergeCell ref="B11:G11"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="37" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>A fast and e ffi cient way of obtaining the average molecular weight of block copolymers via DOSY †</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>PAPER METADATA &amp; EXPERIMENTAL CONDITIONS</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Authors</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Pieter-Jan Voorter, Manfred Wagner, Christine Rosenauer, Jinhuo Dai, Priya Subramanian, Alasdair McKay, Neil R. Cameron, Jasper J. Michels, Tanja Junkers</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="7" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>DOI</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>10.1039/d3py01075a</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Temperature</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Pressure</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Chemicals</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>pMMA, pPEGMEA, pMMA-pPEGMEA block copolymer, deuterated acetone, deuterated chloroform</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-    </row>
-    <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>MALLS and DOSY molecular weight measurements of pMMA homopolymers and pMMA-pPEGMEA block copolymers.</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Other Stats</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>MALLS Mw (g mol-1): 2630 - 135000, DOSYMW (g mol-1) (pMMA calibration): 2740 - 139730, DOSYMW (g mol-1) (pPEGMEA calibration): 1540 - 129610, DOSYMW (g mol-1) (pMMA-pPEGMEA joint calibration): 13810 - 115000</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>TABLE CATEGORISATION</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Contains Scientific Data</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Contains Raw Diffusion Data</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Contains Mark-Houwink Parameters</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Contains Flory Parameters</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Contains Polymer Diffusion Coefficients</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>EXTRACTED RAW TABLE DATA</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr"/>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Sample</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>MALLS. M w (g mol - 1 )</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>DOSYMW (g mol - 1 ) (pMMA)</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>Error (%)</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>DOSYMW (g mol - 1 ) (pPEGMEA)</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>Error (%)</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>DOSYMW (g mol - 1 ) (pMMA-pPEGMEA)</t>
-        </is>
-      </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Error (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>pMMA25</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="n">
-        <v>2630</v>
-      </c>
-      <c r="D22" s="10" t="n">
-        <v>2740</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F22" s="10" t="n">
-        <v>1540</v>
-      </c>
-      <c r="G22" s="10" t="n">
-        <v>71</v>
-      </c>
-      <c r="H22" s="10" t="n">
-        <v>2160</v>
-      </c>
-      <c r="I22" s="10" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>pMMA45</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="n">
-        <v>4910</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>4970</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>3010</v>
-      </c>
-      <c r="G23" s="10" t="n">
-        <v>63</v>
-      </c>
-      <c r="H23" s="10" t="n">
-        <v>3950</v>
-      </c>
-      <c r="I23" s="10" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>pMMA65</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="n">
-        <v>7010</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>7400</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <v>4710</v>
-      </c>
-      <c r="G24" s="10" t="n">
-        <v>49</v>
-      </c>
-      <c r="H24" s="10" t="n">
-        <v>5910</v>
-      </c>
-      <c r="I24" s="10" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>pMMA25-pPEGMEA25</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>10 600</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>14 690</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>10 200</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H25" s="11" t="inlineStr">
-        <is>
-          <t>11 810</t>
-        </is>
-      </c>
-      <c r="I25" s="10" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>pMMA25-pPEGMEA50</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>23 000</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>32 600</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>25 100</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>26 430</t>
-        </is>
-      </c>
-      <c r="I26" s="10" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>pMMA25-pPEGMEA75</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>45 400</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>56 160</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>46 340</t>
-        </is>
-      </c>
-      <c r="G27" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" s="11" t="inlineStr">
-        <is>
-          <t>45 780</t>
-        </is>
-      </c>
-      <c r="I27" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>pMMA45-pPEGMEA25</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>18 000</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>22 580</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>16 580</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="H28" s="11" t="inlineStr">
-        <is>
-          <t>18 230</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>pMMA45-pPEGMEA50</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>34 500</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>43 860</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>35 070</t>
-        </is>
-      </c>
-      <c r="G29" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" s="11" t="inlineStr">
-        <is>
-          <t>35 670</t>
-        </is>
-      </c>
-      <c r="I29" s="10" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>pMMA45-pPEGMEA75</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>68 400</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>78 110</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>67 250</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" s="11" t="inlineStr">
-        <is>
-          <t>63 900</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>pMMA65-pPEGMEA25</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>31 500</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>41 540</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>32 980</t>
-        </is>
-      </c>
-      <c r="G31" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>33 760</t>
-        </is>
-      </c>
-      <c r="I31" s="10" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>pMMA65-pPEGMEA50</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>91 100</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>90 450</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>79 350</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="H32" s="11" t="inlineStr">
-        <is>
-          <t>84 100</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>pMMA65-pPEGMEA75</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>135 000</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>139 730</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>129 610</t>
-        </is>
-      </c>
-      <c r="G33" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H33" s="11" t="inlineStr">
-        <is>
-          <t>115 000</t>
-        </is>
-      </c>
-      <c r="I33" s="10" t="n">
-        <v>18</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="A1:G2"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B15:G15"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="B6:G6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4041,7 +5547,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>A fast and e ffi cient way of obtaining the average molecular weight of block copolymers via DOSY †</t>
+          <t>test7</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4080,11 +5586,7 @@
           <t>Authors</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Pieter-Jan Voorter, Manfred Wagner, Christine Rosenauer, Jinhuo Dai, Priya Subramanian, Alasdair McKay, Neil R. Cameron, Jasper J. Michels, Tanja Junkers</t>
-        </is>
-      </c>
+      <c r="B5" s="6" t="inlineStr"/>
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="n"/>
@@ -4097,11 +5599,7 @@
           <t>DOI</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>10.1039/d3py01075a</t>
-        </is>
-      </c>
+      <c r="B6" s="6" t="inlineStr"/>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
@@ -4350,454 +5848,454 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>pBA60</t>
         </is>
       </c>
-      <c r="C22" s="10" t="n">
+      <c r="C22" s="13" t="n">
         <v>5400</v>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D22" s="13" t="n">
         <v>5410</v>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="E22" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="10" t="n">
+      <c r="F22" s="13" t="n">
         <v>4020</v>
       </c>
-      <c r="G22" s="10" t="n">
+      <c r="G22" s="13" t="n">
         <v>34</v>
       </c>
-      <c r="H22" s="10" t="n">
+      <c r="H22" s="13" t="n">
         <v>4930</v>
       </c>
-      <c r="I22" s="10" t="n">
+      <c r="I22" s="13" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n">
+      <c r="A23" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>pBA80</t>
         </is>
       </c>
-      <c r="C23" s="10" t="n">
+      <c r="C23" s="13" t="n">
         <v>7400</v>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D23" s="13" t="n">
         <v>7370</v>
       </c>
-      <c r="E23" s="10" t="n">
+      <c r="E23" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="10" t="n">
+      <c r="F23" s="13" t="n">
         <v>5930</v>
       </c>
-      <c r="G23" s="10" t="n">
+      <c r="G23" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="H23" s="10" t="n">
+      <c r="H23" s="13" t="n">
         <v>6900</v>
       </c>
-      <c r="I23" s="10" t="n">
+      <c r="I23" s="13" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n">
+      <c r="A24" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>pBA100</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>11 800</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>11 820</t>
         </is>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="E24" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>10 770</t>
         </is>
       </c>
-      <c r="G24" s="10" t="n">
+      <c r="G24" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H24" s="12" t="inlineStr">
         <is>
           <t>11 550</t>
         </is>
       </c>
-      <c r="I24" s="10" t="n">
+      <c r="I24" s="13" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n">
+      <c r="A25" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>pBA60-pPEGMEA25</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>13 600</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>14 190</t>
         </is>
       </c>
-      <c r="E25" s="10" t="n">
+      <c r="E25" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>13 560</t>
         </is>
       </c>
-      <c r="G25" s="10" t="n">
+      <c r="G25" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H25" s="12" t="inlineStr">
         <is>
           <t>14 100</t>
         </is>
       </c>
-      <c r="I25" s="10" t="n">
+      <c r="I25" s="13" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>pBA60-pPEGMEA50</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>22 700</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>22 900</t>
         </is>
       </c>
-      <c r="E26" s="10" t="n">
+      <c r="E26" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="12" t="inlineStr">
         <is>
           <t>24 820</t>
         </is>
       </c>
-      <c r="G26" s="10" t="n">
+      <c r="G26" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H26" s="12" t="inlineStr">
         <is>
           <t>23 760</t>
         </is>
       </c>
-      <c r="I26" s="10" t="n">
+      <c r="I26" s="13" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n">
+      <c r="A27" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>pBA60-pPEGMEA75</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>30 900</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>29 660</t>
         </is>
       </c>
-      <c r="E27" s="10" t="n">
+      <c r="E27" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>34 410</t>
         </is>
       </c>
-      <c r="G27" s="10" t="n">
+      <c r="G27" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>31 500</t>
         </is>
       </c>
-      <c r="I27" s="10" t="n">
+      <c r="I27" s="13" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="n">
+      <c r="A28" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>pBA80-pPEGMEA25</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>14 700</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>14 310</t>
         </is>
       </c>
-      <c r="E28" s="10" t="n">
+      <c r="E28" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>13 700</t>
         </is>
       </c>
-      <c r="G28" s="10" t="n">
+      <c r="G28" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H28" s="12" t="inlineStr">
         <is>
           <t>14 230</t>
         </is>
       </c>
-      <c r="I28" s="10" t="n">
+      <c r="I28" s="13" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
+      <c r="A29" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>pBA80-pPEGMEA50</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>24 300</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>21 230</t>
         </is>
       </c>
-      <c r="E29" s="10" t="n">
+      <c r="E29" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>22 560</t>
         </is>
       </c>
-      <c r="G29" s="10" t="n">
+      <c r="G29" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>21 890</t>
         </is>
       </c>
-      <c r="I29" s="10" t="n">
+      <c r="I29" s="13" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n">
+      <c r="A30" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>pBA80-pPEGMEA75</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>33 400</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>25 960</t>
         </is>
       </c>
-      <c r="E30" s="10" t="n">
+      <c r="E30" s="13" t="n">
         <v>29</v>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F30" s="12" t="inlineStr">
         <is>
           <t>29 070</t>
         </is>
       </c>
-      <c r="G30" s="10" t="n">
+      <c r="G30" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="H30" s="12" t="inlineStr">
         <is>
           <t>27 240</t>
         </is>
       </c>
-      <c r="I30" s="10" t="n">
+      <c r="I30" s="13" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n">
+      <c r="A31" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>pBA100-pPEGMEA25</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>15 100</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>14 070</t>
         </is>
       </c>
-      <c r="E31" s="10" t="n">
+      <c r="E31" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F31" s="12" t="inlineStr">
         <is>
           <t>13 410</t>
         </is>
       </c>
-      <c r="G31" s="10" t="n">
+      <c r="G31" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>13 960</t>
         </is>
       </c>
-      <c r="I31" s="10" t="n">
+      <c r="I31" s="13" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n">
+      <c r="A32" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>pBA100-pPEGMEA50</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>25 400</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>22 410</t>
         </is>
       </c>
-      <c r="E32" s="10" t="n">
+      <c r="E32" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="12" t="inlineStr">
         <is>
           <t>24 150</t>
         </is>
       </c>
-      <c r="G32" s="10" t="n">
+      <c r="G32" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H32" s="12" t="inlineStr">
         <is>
           <t>23 200</t>
         </is>
       </c>
-      <c r="I32" s="10" t="n">
+      <c r="I32" s="13" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="n">
+      <c r="A33" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>pBA100-pPEGMEA75</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>35 500</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>27 890</t>
         </is>
       </c>
-      <c r="E33" s="10" t="n">
+      <c r="E33" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F33" s="12" t="inlineStr">
         <is>
           <t>31 830</t>
         </is>
       </c>
-      <c r="G33" s="10" t="n">
+      <c r="G33" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H33" s="12" t="inlineStr">
         <is>
           <t>29 450</t>
         </is>
       </c>
-      <c r="I33" s="10" t="n">
+      <c r="I33" s="13" t="n">
         <v>8</v>
       </c>
     </row>
